--- a/artfynd/A 64668-2021 artfynd.xlsx
+++ b/artfynd/A 64668-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64668-2021 artfynd.xlsx
+++ b/artfynd/A 64668-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,117 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120506366</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Järvdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>431581</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7004730</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64668-2021 artfynd.xlsx
+++ b/artfynd/A 64668-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104305743</v>
+        <v>120506366</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
+        <v>57348</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,11 +937,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431580.8247818049</v>
+        <v>431581</v>
       </c>
       <c r="R4" t="n">
-        <v>7004729.56540584</v>
+        <v>7004730</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +975,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,126 +1000,15 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Maria Danvind</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>120506366</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Järvdalen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>431581</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7004730</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64668-2021 artfynd.xlsx
+++ b/artfynd/A 64668-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101306724</v>
+        <v>120506205</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spjätten SV, Jmt</t>
+          <t>Järvdalen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431591</v>
+        <v>431598</v>
       </c>
       <c r="R2" t="n">
-        <v>7004643</v>
+        <v>7004912</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +763,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104305745</v>
+        <v>120506366</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,11 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431587.5939879901</v>
+        <v>431581</v>
       </c>
       <c r="R3" t="n">
-        <v>7004578.918813146</v>
+        <v>7004730</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +875,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -901,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120506366</v>
+        <v>104305745</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,7 +918,11 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431581</v>
+        <v>431587</v>
       </c>
       <c r="R4" t="n">
-        <v>7004730</v>
+        <v>7004579</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,17 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,15 +980,855 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112449231</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Spjätten SV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>431595</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7004848</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Maria Danvind</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112449312</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Spjätten SV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>431577</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7004600</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack på 2 träd</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112449335</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Spjätten SV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>431541</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7004380</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112449366</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spjätten SV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>431524</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7004376</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112449392</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Spjätten SV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>431518</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7004371</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112449422</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Spjätten SV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>431448</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7004292</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112828393</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Spjätten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>431620</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7004602</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112828394</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Spjätten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>431562</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7004464</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64668-2021 artfynd.xlsx
+++ b/artfynd/A 64668-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120506205</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120506366</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305745</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112449231</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112449312</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112449335</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112449366</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112449392</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112449422</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112828393</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,8 +1884,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112828394</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>